--- a/exports/trend_1d/NBCC_full_report.xlsx
+++ b/exports/trend_1d/NBCC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>35.87</v>
+        <v>31.53</v>
       </c>
       <c r="I2" t="n">
         <v>35.61382085386913</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.54</v>
+        <v>-13.45</v>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>16.66</v>
       </c>
       <c r="M2" t="n">
         <v>0.92</v>
       </c>
       <c r="N2" t="n">
-        <v>3.81</v>
+        <v>12.1</v>
       </c>
       <c r="O2" t="n">
         <v>0.66</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>21.32</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42060</v>
+        <v>42061</v>
       </c>
       <c r="H3" t="n">
-        <v>37.53</v>
+        <v>37.69</v>
       </c>
       <c r="I3" t="n">
         <v>37.60580832518656</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-19.03</v>
+        <v>-19.54</v>
       </c>
       <c r="L3" t="n">
-        <v>21.57</v>
+        <v>22.77</v>
       </c>
       <c r="M3" t="n">
         <v>2.32</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H4" t="n">
-        <v>39.77</v>
+        <v>38.71</v>
       </c>
       <c r="I4" t="n">
         <v>39.60571842534852</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>5.52</v>
+        <v>2.71</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.44</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42177</v>
+        <v>42178</v>
       </c>
       <c r="H5" t="n">
-        <v>34.77</v>
+        <v>35.51</v>
       </c>
       <c r="I5" t="n">
         <v>35.42880034541334</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>10.18</v>
+        <v>8.27</v>
       </c>
       <c r="L5" t="n">
         <v>3.46</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.09</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>47.33</v>
+        <v>44.33</v>
       </c>
       <c r="I6" t="n">
         <v>45.43898452152938</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6" t="n">
-        <v>33.29</v>
+        <v>24.84</v>
       </c>
       <c r="L6" t="n">
         <v>2.68</v>
@@ -783,7 +854,7 @@
         <v>4.88</v>
       </c>
       <c r="N6" t="n">
-        <v>4.24</v>
+        <v>6.34</v>
       </c>
       <c r="O6" t="n">
         <v>2.13</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>21.44</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42331</v>
+        <v>42332</v>
       </c>
       <c r="H7" t="n">
-        <v>41.78</v>
+        <v>44.19</v>
       </c>
       <c r="I7" t="n">
         <v>43.06020727782774</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>0.32</v>
       </c>
       <c r="L7" t="n">
         <v>9.59</v>
@@ -840,7 +923,7 @@
         <v>4.29</v>
       </c>
       <c r="N7" t="n">
-        <v>4.08</v>
+        <v>5.77</v>
       </c>
       <c r="O7" t="n">
         <v>-6.34</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.64</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>41.91</v>
+        <v>40.31</v>
       </c>
       <c r="I8" t="n">
         <v>41.33406980114946</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.16</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>8.279999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>2.19</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>3.82</v>
       </c>
       <c r="O8" t="n">
         <v>5.77</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.55</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42444</v>
+        <v>42445</v>
       </c>
       <c r="H9" t="n">
-        <v>40.8</v>
+        <v>42.58</v>
       </c>
       <c r="I9" t="n">
         <v>42.47294666595927</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.22</v>
+        <v>-5.63</v>
       </c>
       <c r="L9" t="n">
         <v>9.029999999999999</v>
@@ -954,7 +1061,7 @@
         <v>2.73</v>
       </c>
       <c r="N9" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="O9" t="n">
         <v>-3.82</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.37</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42513</v>
+        <v>42514</v>
       </c>
       <c r="H10" t="n">
-        <v>42.58</v>
+        <v>41.74</v>
       </c>
       <c r="I10" t="n">
         <v>41.7543620678773</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-1.97</v>
       </c>
       <c r="L10" t="n">
         <v>4.58</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.99</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42556</v>
+        <v>42558</v>
       </c>
       <c r="H11" t="n">
-        <v>43.29</v>
+        <v>47.9</v>
       </c>
       <c r="I11" t="n">
         <v>43.9864711558085</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.71</v>
+        <v>-14.76</v>
       </c>
       <c r="L11" t="n">
-        <v>6.49</v>
+        <v>18.57</v>
       </c>
       <c r="M11" t="n">
         <v>1.97</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>10.65</v>
       </c>
       <c r="O11" t="n">
         <v>-1.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42653</v>
+        <v>42656</v>
       </c>
       <c r="H12" t="n">
-        <v>58.19</v>
+        <v>57.23</v>
       </c>
       <c r="I12" t="n">
         <v>57.25874434533235</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K12" t="n">
-        <v>21.48</v>
+        <v>19.48</v>
       </c>
       <c r="L12" t="n">
         <v>7.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.56</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H13" t="n">
-        <v>53.1</v>
+        <v>56.33</v>
       </c>
       <c r="I13" t="n">
         <v>53.14796910073319</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
-        <v>7.22</v>
+        <v>1.57</v>
       </c>
       <c r="L13" t="n">
         <v>4.02</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42782</v>
+        <v>42783</v>
       </c>
       <c r="H14" t="n">
-        <v>64.28</v>
+        <v>58.37</v>
       </c>
       <c r="I14" t="n">
         <v>60.62457697117414</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14" t="n">
-        <v>14.11</v>
+        <v>3.62</v>
       </c>
       <c r="L14" t="n">
-        <v>5.15</v>
+        <v>7.86</v>
       </c>
       <c r="M14" t="n">
         <v>0.61</v>
       </c>
       <c r="N14" t="n">
-        <v>4.76</v>
+        <v>9.19</v>
       </c>
       <c r="O14" t="n">
         <v>6.08</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.77</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42843</v>
+        <v>42844</v>
       </c>
       <c r="H15" t="n">
-        <v>60.37</v>
+        <v>60.67</v>
       </c>
       <c r="I15" t="n">
         <v>60.52912935098462</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.43</v>
+        <v>-3.94</v>
       </c>
       <c r="L15" t="n">
         <v>10.62</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.15</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H16" t="n">
-        <v>63.07</v>
+        <v>60.32</v>
       </c>
       <c r="I16" t="n">
         <v>61.9078675712536</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>3.96</v>
+        <v>-0.58</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.09</v>
       </c>
       <c r="M16" t="n">
         <v>1.68</v>
       </c>
       <c r="N16" t="n">
-        <v>3.08</v>
+        <v>4.36</v>
       </c>
       <c r="O16" t="n">
         <v>0.5</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.19</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42888</v>
+        <v>42891</v>
       </c>
       <c r="H17" t="n">
-        <v>65.22</v>
+        <v>67.05</v>
       </c>
       <c r="I17" t="n">
         <v>66.64378417998785</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.119999999999999</v>
+        <v>-11.16</v>
       </c>
       <c r="L17" t="n">
-        <v>10.25</v>
+        <v>12.62</v>
       </c>
       <c r="M17" t="n">
         <v>1.69</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>10.3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H18" t="n">
-        <v>69.29000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="I18" t="n">
         <v>67.45842416907719</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K18" t="n">
-        <v>3.34</v>
+        <v>-3.03</v>
       </c>
       <c r="L18" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.22</v>
+        <v>6.16</v>
       </c>
       <c r="O18" t="n">
         <v>2.81</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.58</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42997</v>
+        <v>42998</v>
       </c>
       <c r="H19" t="n">
-        <v>71.67</v>
+        <v>73.39</v>
       </c>
       <c r="I19" t="n">
         <v>72.22512544971352</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.23</v>
+        <v>-12.87</v>
       </c>
       <c r="L19" t="n">
-        <v>12.27</v>
+        <v>13.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.91</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H20" t="n">
-        <v>70.8</v>
+        <v>69.17</v>
       </c>
       <c r="I20" t="n">
         <v>69.44588249863178</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.53</v>
+        <v>-5.75</v>
       </c>
       <c r="L20" t="n">
-        <v>5.53</v>
+        <v>6.35</v>
       </c>
       <c r="M20" t="n">
         <v>0.35</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H21" t="n">
-        <v>73.75</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>76.41567344338291</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.62</v>
+        <v>-16.6</v>
       </c>
       <c r="L21" t="n">
-        <v>9.109999999999999</v>
+        <v>17.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.59</v>
       </c>
       <c r="N21" t="n">
-        <v>1.49</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>-2.3</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43081</v>
+        <v>43082</v>
       </c>
       <c r="H22" t="n">
-        <v>83.72</v>
+        <v>82.02</v>
       </c>
       <c r="I22" t="n">
         <v>82.86579676330425</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K22" t="n">
-        <v>3.81</v>
+        <v>1.7</v>
       </c>
       <c r="L22" t="n">
         <v>7.72</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>11.41</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H23" t="n">
-        <v>66.33</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>67.45404466229309</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K23" t="n">
-        <v>19.13</v>
+        <v>14.57</v>
       </c>
       <c r="L23" t="n">
         <v>4.97</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>4.73</v>
       </c>
       <c r="N23" t="n">
         <v>6.24</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>10.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H24" t="n">
-        <v>66.47</v>
+        <v>65.53</v>
       </c>
       <c r="I24" t="n">
         <v>65.72558979408775</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.14</v>
+        <v>-6.48</v>
       </c>
       <c r="L24" t="n">
-        <v>6.28</v>
+        <v>7.99</v>
       </c>
       <c r="M24" t="n">
         <v>2.83</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.73</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43313</v>
+        <v>43314</v>
       </c>
       <c r="H25" t="n">
-        <v>47.2</v>
+        <v>49.87</v>
       </c>
       <c r="I25" t="n">
         <v>47.68530912498058</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" t="n">
-        <v>27.97</v>
+        <v>23.9</v>
       </c>
       <c r="L25" t="n">
         <v>3.97</v>
@@ -1866,7 +2165,7 @@
         <v>1.89</v>
       </c>
       <c r="N25" t="n">
-        <v>4.78</v>
+        <v>5.66</v>
       </c>
       <c r="O25" t="n">
         <v>-1.41</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>15.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H26" t="n">
-        <v>46.13</v>
+        <v>45.3</v>
       </c>
       <c r="I26" t="n">
         <v>46.03294078370021</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.5</v>
+        <v>-9.16</v>
       </c>
       <c r="L26" t="n">
-        <v>8.02</v>
+        <v>11.43</v>
       </c>
       <c r="M26" t="n">
         <v>1.9</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.12</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H27" t="n">
-        <v>39.23</v>
+        <v>41.7</v>
       </c>
       <c r="I27" t="n">
         <v>40.83025727126201</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K27" t="n">
-        <v>13.4</v>
+        <v>7.95</v>
       </c>
       <c r="L27" t="n">
         <v>6.34</v>
@@ -1980,7 +2303,7 @@
         <v>3.54</v>
       </c>
       <c r="N27" t="n">
-        <v>5.81</v>
+        <v>6.3</v>
       </c>
       <c r="O27" t="n">
         <v>-1.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>17.45</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43425</v>
+        <v>43426</v>
       </c>
       <c r="H28" t="n">
-        <v>39.13</v>
+        <v>38.43</v>
       </c>
       <c r="I28" t="n">
         <v>38.66569167705762</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.16</v>
+        <v>-7.84</v>
       </c>
       <c r="L28" t="n">
-        <v>7.51</v>
+        <v>8.08</v>
       </c>
       <c r="M28" t="n">
         <v>1.44</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>14.86</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H29" t="n">
-        <v>35.6</v>
+        <v>39.17</v>
       </c>
       <c r="I29" t="n">
         <v>37.75347337458889</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>7.36</v>
+        <v>-1.93</v>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>3.12</v>
       </c>
       <c r="M29" t="n">
         <v>2.19</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>10.03</v>
       </c>
       <c r="O29" t="n">
         <v>-1.79</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.99</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43500</v>
+        <v>43501</v>
       </c>
       <c r="H30" t="n">
-        <v>37.47</v>
+        <v>35.6</v>
       </c>
       <c r="I30" t="n">
         <v>36.98872294770136</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.34</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>10.9</v>
@@ -2151,7 +2510,7 @@
         <v>1.28</v>
       </c>
       <c r="N30" t="n">
-        <v>4.12</v>
+        <v>4.99</v>
       </c>
       <c r="O30" t="n">
         <v>10.03</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>15.08</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H31" t="n">
-        <v>36.7</v>
+        <v>38.33</v>
       </c>
       <c r="I31" t="n">
         <v>37.56606987763593</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.09</v>
+        <v>-7.67</v>
       </c>
       <c r="L31" t="n">
-        <v>5.42</v>
+        <v>8.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.48</v>
       </c>
       <c r="N31" t="n">
-        <v>4.17</v>
+        <v>4.44</v>
       </c>
       <c r="O31" t="n">
         <v>-4.99</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.23</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H32" t="n">
-        <v>41.07</v>
+        <v>39.9</v>
       </c>
       <c r="I32" t="n">
         <v>40.01979818446854</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K32" t="n">
-        <v>7.15</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
         <v>4.07</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.64</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H33" t="n">
-        <v>38.4</v>
+        <v>40.77</v>
       </c>
       <c r="I33" t="n">
         <v>39.09253622366457</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K33" t="n">
-        <v>3.76</v>
+        <v>-2.18</v>
       </c>
       <c r="L33" t="n">
         <v>2.93</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>15.66</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43633</v>
+        <v>43634</v>
       </c>
       <c r="H34" t="n">
-        <v>37.77</v>
+        <v>37.67</v>
       </c>
       <c r="I34" t="n">
         <v>37.71091532992517</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.36</v>
+        <v>-7.6</v>
       </c>
       <c r="L34" t="n">
-        <v>7.78</v>
+        <v>8.83</v>
       </c>
       <c r="M34" t="n">
         <v>1.45</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.25</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43714</v>
+        <v>43717</v>
       </c>
       <c r="H35" t="n">
-        <v>23.83</v>
+        <v>25</v>
       </c>
       <c r="I35" t="n">
         <v>24.75132302098991</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K35" t="n">
-        <v>36.74</v>
+        <v>33.63</v>
       </c>
       <c r="L35" t="n">
         <v>11.49</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>21.16</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43795</v>
+        <v>43796</v>
       </c>
       <c r="H36" t="n">
-        <v>24.27</v>
+        <v>23.83</v>
       </c>
       <c r="I36" t="n">
         <v>24.08581319098318</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.92</v>
+        <v>-4.68</v>
       </c>
       <c r="L36" t="n">
         <v>16.52</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.44</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H37" t="n">
-        <v>24.9</v>
+        <v>26.07</v>
       </c>
       <c r="I37" t="n">
         <v>25.19258874949457</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.49</v>
+        <v>-9.4</v>
       </c>
       <c r="L37" t="n">
-        <v>10.24</v>
+        <v>11.08</v>
       </c>
       <c r="M37" t="n">
         <v>2.92</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>13.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H38" t="n">
-        <v>22.9</v>
+        <v>22.47</v>
       </c>
       <c r="I38" t="n">
         <v>22.81129219952041</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.16</v>
+        <v>-13.81</v>
       </c>
       <c r="L38" t="n">
-        <v>13.04</v>
+        <v>14.58</v>
       </c>
       <c r="M38" t="n">
         <v>0.68</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.13</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H39" t="n">
-        <v>13.7</v>
+        <v>15.23</v>
       </c>
       <c r="I39" t="n">
         <v>13.74823619585937</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K39" t="n">
-        <v>39.03</v>
+        <v>32.22</v>
       </c>
       <c r="L39" t="n">
         <v>3.38</v>
@@ -2664,7 +3131,7 @@
         <v>4.66</v>
       </c>
       <c r="N39" t="n">
-        <v>10.07</v>
+        <v>11.17</v>
       </c>
       <c r="O39" t="n">
         <v>-1.88</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>27.11</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43955</v>
+        <v>43956</v>
       </c>
       <c r="H40" t="n">
-        <v>12.8</v>
+        <v>12.57</v>
       </c>
       <c r="I40" t="n">
         <v>12.7580547753474</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>-15.96</v>
+        <v>-17.47</v>
       </c>
       <c r="L40" t="n">
-        <v>17.47</v>
+        <v>17.73</v>
       </c>
       <c r="M40" t="n">
         <v>4.24</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>23.58</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H41" t="n">
-        <v>12.7</v>
+        <v>14.87</v>
       </c>
       <c r="I41" t="n">
         <v>12.98906587529427</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.03</v>
+        <v>-18.3</v>
       </c>
       <c r="L41" t="n">
-        <v>3.98</v>
+        <v>19.57</v>
       </c>
       <c r="M41" t="n">
         <v>4.49</v>
       </c>
       <c r="N41" t="n">
-        <v>4.94</v>
+        <v>17.09</v>
       </c>
       <c r="O41" t="n">
         <v>-1.8</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>19.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H42" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="I42" t="n">
         <v>15.59361615785521</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K42" t="n">
-        <v>5.58</v>
+        <v>3.56</v>
       </c>
       <c r="L42" t="n">
         <v>11.9</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.71</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44055</v>
+        <v>44056</v>
       </c>
       <c r="H43" t="n">
-        <v>16.4</v>
+        <v>17.37</v>
       </c>
       <c r="I43" t="n">
         <v>17.07185014583522</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.49</v>
+        <v>-12.79</v>
       </c>
       <c r="L43" t="n">
-        <v>7.6</v>
+        <v>14.29</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.33</v>
+        <v>5.91</v>
       </c>
       <c r="O43" t="n">
         <v>-1.91</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>13.03</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H44" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="I44" t="n">
         <v>17.38126853178422</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>0.17</v>
+        <v>-0.4</v>
       </c>
       <c r="L44" t="n">
         <v>5.41</v>
       </c>
       <c r="M44" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="N44" t="n">
         <v>5.31</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H45" t="n">
-        <v>15.83</v>
+        <v>16.33</v>
       </c>
       <c r="I45" t="n">
         <v>16.29544115150165</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K45" t="n">
-        <v>8.5</v>
+        <v>5.61</v>
       </c>
       <c r="L45" t="n">
         <v>6.94</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H46" t="n">
-        <v>20.27</v>
+        <v>18.43</v>
       </c>
       <c r="I46" t="n">
         <v>18.71629489276209</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K46" t="n">
-        <v>24.13</v>
+        <v>12.86</v>
       </c>
       <c r="L46" t="n">
         <v>2.02</v>
@@ -3063,7 +3614,7 @@
         <v>0.62</v>
       </c>
       <c r="N46" t="n">
-        <v>3.05</v>
+        <v>9.08</v>
       </c>
       <c r="O46" t="n">
         <v>3.16</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>20.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44200</v>
+        <v>44201</v>
       </c>
       <c r="H47" t="n">
-        <v>20.57</v>
+        <v>21.77</v>
       </c>
       <c r="I47" t="n">
         <v>21.27230042085879</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.61</v>
+        <v>-18.12</v>
       </c>
       <c r="L47" t="n">
-        <v>12.48</v>
+        <v>19.21</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>15.6</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H48" t="n">
-        <v>31.1</v>
+        <v>27.53</v>
       </c>
       <c r="I48" t="n">
         <v>28.29629347990894</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K48" t="n">
-        <v>42.86</v>
+        <v>26.46</v>
       </c>
       <c r="L48" t="n">
         <v>9.369999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>3.19</v>
+        <v>4.18</v>
       </c>
       <c r="N48" t="n">
-        <v>5.65</v>
+        <v>11.48</v>
       </c>
       <c r="O48" t="n">
         <v>5.83</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>23.33</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H49" t="n">
-        <v>29.33</v>
+        <v>31.83</v>
       </c>
       <c r="I49" t="n">
         <v>31.04329310500252</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.54</v>
+        <v>-15.62</v>
       </c>
       <c r="L49" t="n">
-        <v>10.06</v>
+        <v>17.22</v>
       </c>
       <c r="M49" t="n">
         <v>1.94</v>
       </c>
       <c r="N49" t="n">
-        <v>4.28</v>
+        <v>8.52</v>
       </c>
       <c r="O49" t="n">
         <v>-11.48</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>17.13</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H50" t="n">
-        <v>33.53</v>
+        <v>33.23</v>
       </c>
       <c r="I50" t="n">
         <v>33.32267132379543</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>5.34</v>
+        <v>4.4</v>
       </c>
       <c r="L50" t="n">
         <v>7.63</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.16</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44467</v>
+        <v>44468</v>
       </c>
       <c r="H51" t="n">
-        <v>31.27</v>
+        <v>32.1</v>
       </c>
       <c r="I51" t="n">
         <v>31.67838920383292</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K51" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="L51" t="n">
         <v>5.84</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>10.84</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H52" t="n">
-        <v>30.3</v>
+        <v>29.77</v>
       </c>
       <c r="I52" t="n">
         <v>29.91056057075776</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.61</v>
+        <v>-7.26</v>
       </c>
       <c r="L52" t="n">
-        <v>6.54</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M52" t="n">
         <v>1.16</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.09</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H53" t="n">
-        <v>29.73</v>
+        <v>31.13</v>
       </c>
       <c r="I53" t="n">
         <v>30.23601816849962</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K53" t="n">
-        <v>0.13</v>
+        <v>-4.57</v>
       </c>
       <c r="L53" t="n">
         <v>10.41</v>
@@ -3462,7 +4097,7 @@
         <v>5.58</v>
       </c>
       <c r="N53" t="n">
-        <v>4.47</v>
+        <v>4.71</v>
       </c>
       <c r="O53" t="n">
         <v>-1.75</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>12</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H54" t="n">
-        <v>28.47</v>
+        <v>27.33</v>
       </c>
       <c r="I54" t="n">
         <v>27.87268968091979</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.539999999999999</v>
+        <v>-12.21</v>
       </c>
       <c r="L54" t="n">
-        <v>9.41</v>
+        <v>13.27</v>
       </c>
       <c r="M54" t="n">
-        <v>0.88</v>
+        <v>1.19</v>
       </c>
       <c r="N54" t="n">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
         <v>4.71</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>13.07</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H55" t="n">
-        <v>30.67</v>
+        <v>31.13</v>
       </c>
       <c r="I55" t="n">
         <v>30.81278886519102</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.22</v>
+        <v>-13.9</v>
       </c>
       <c r="L55" t="n">
-        <v>14.78</v>
+        <v>15.37</v>
       </c>
       <c r="M55" t="n">
         <v>1.72</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H56" t="n">
-        <v>31.93</v>
+        <v>30.07</v>
       </c>
       <c r="I56" t="n">
         <v>31.9229191835598</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>2.57</v>
+        <v>-3.41</v>
       </c>
       <c r="L56" t="n">
-        <v>3.31</v>
+        <v>4.27</v>
       </c>
       <c r="M56" t="n">
         <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>5.33</v>
+        <v>5.83</v>
       </c>
       <c r="O56" t="n">
         <v>1.5</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>16.7</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H57" t="n">
-        <v>26.63</v>
+        <v>27.33</v>
       </c>
       <c r="I57" t="n">
         <v>26.96015729645873</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K57" t="n">
-        <v>11.44</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L57" t="n">
         <v>6.98</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.42</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H58" t="n">
-        <v>24.83</v>
+        <v>24.2</v>
       </c>
       <c r="I58" t="n">
         <v>24.67332440059141</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>-9.15</v>
+        <v>-11.45</v>
       </c>
       <c r="L58" t="n">
-        <v>9.99</v>
+        <v>13.54</v>
       </c>
       <c r="M58" t="n">
         <v>1.16</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.86</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H59" t="n">
-        <v>19.4</v>
+        <v>21.23</v>
       </c>
       <c r="I59" t="n">
         <v>21.04133372542565</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K59" t="n">
-        <v>19.83</v>
+        <v>12.27</v>
       </c>
       <c r="L59" t="n">
         <v>3.6</v>
@@ -3804,7 +4511,7 @@
         <v>2.81</v>
       </c>
       <c r="N59" t="n">
-        <v>4.37</v>
+        <v>9.43</v>
       </c>
       <c r="O59" t="n">
         <v>-2.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>14.52</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H60" t="n">
-        <v>22.13</v>
+        <v>20.97</v>
       </c>
       <c r="I60" t="n">
         <v>22.08888868418381</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K60" t="n">
-        <v>4.24</v>
+        <v>-1.22</v>
       </c>
       <c r="L60" t="n">
         <v>8.289999999999999</v>
@@ -3861,7 +4580,7 @@
         <v>3.68</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>5.24</v>
       </c>
       <c r="O60" t="n">
         <v>9.43</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>13.82</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H61" t="n">
-        <v>21.63</v>
+        <v>22.27</v>
       </c>
       <c r="I61" t="n">
         <v>21.96046161482111</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.15</v>
+        <v>-6.2</v>
       </c>
       <c r="L61" t="n">
-        <v>6.82</v>
+        <v>7.3</v>
       </c>
       <c r="M61" t="n">
         <v>1.83</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.31</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H62" t="n">
-        <v>25.97</v>
+        <v>24.77</v>
       </c>
       <c r="I62" t="n">
         <v>25.08849620273023</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K62" t="n">
-        <v>16.61</v>
+        <v>11.23</v>
       </c>
       <c r="L62" t="n">
         <v>3.01</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>18.53</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44986</v>
+        <v>44987</v>
       </c>
       <c r="H63" t="n">
-        <v>22.57</v>
+        <v>24.13</v>
       </c>
       <c r="I63" t="n">
         <v>23.92957740097953</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K63" t="n">
-        <v>8.880000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="L63" t="n">
         <v>11.3</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>11.7</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H64" t="n">
-        <v>23.47</v>
+        <v>22.8</v>
       </c>
       <c r="I64" t="n">
         <v>22.91372827028525</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.74</v>
+        <v>-5.51</v>
       </c>
       <c r="L64" t="n">
         <v>6.22</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.91</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45013</v>
+        <v>45014</v>
       </c>
       <c r="H65" t="n">
-        <v>20.73</v>
+        <v>23.5</v>
       </c>
       <c r="I65" t="n">
         <v>23.42171692778888</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
-        <v>9.08</v>
+        <v>-3.07</v>
       </c>
       <c r="L65" t="n">
-        <v>2.76</v>
+        <v>7.59</v>
       </c>
       <c r="M65" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="N65" t="n">
-        <v>0.44</v>
+        <v>13.36</v>
       </c>
       <c r="O65" t="n">
         <v>-2.85</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>17.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45104</v>
+        <v>45105</v>
       </c>
       <c r="H66" t="n">
-        <v>26.4</v>
+        <v>25.63</v>
       </c>
       <c r="I66" t="n">
         <v>26.38369650113477</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K66" t="n">
-        <v>12.34</v>
+        <v>9.06</v>
       </c>
       <c r="L66" t="n">
         <v>10.94</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.27</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H67" t="n">
-        <v>27.9</v>
+        <v>28.5</v>
       </c>
       <c r="I67" t="n">
         <v>28.2633916477259</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.859999999999999</v>
+        <v>-11.2</v>
       </c>
       <c r="L67" t="n">
-        <v>10.42</v>
+        <v>13.81</v>
       </c>
       <c r="M67" t="n">
         <v>1.02</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H68" t="n">
-        <v>98.63</v>
+        <v>88.77</v>
       </c>
       <c r="I68" t="n">
         <v>90.46352639180438</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K68" t="n">
-        <v>246.07</v>
+        <v>211.47</v>
       </c>
       <c r="L68" t="n">
         <v>2</v>
@@ -4317,7 +5132,7 @@
         <v>2.21</v>
       </c>
       <c r="N68" t="n">
-        <v>9.210000000000001</v>
+        <v>10</v>
       </c>
       <c r="O68" t="n">
         <v>2.15</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>8</v>
+      </c>
+      <c r="U68" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>31.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H69" t="n">
-        <v>84.40000000000001</v>
+        <v>92.23</v>
       </c>
       <c r="I69" t="n">
         <v>86.48973137330799</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K69" t="n">
-        <v>4.92</v>
+        <v>-3.9</v>
       </c>
       <c r="L69" t="n">
         <v>10.99</v>
@@ -4374,7 +5201,7 @@
         <v>4.97</v>
       </c>
       <c r="N69" t="n">
-        <v>4.99</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="O69" t="n">
         <v>-10</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>18.9</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H70" t="n">
-        <v>90.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I70" t="n">
         <v>86.90319956724019</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.98</v>
+        <v>-6</v>
       </c>
       <c r="L70" t="n">
         <v>14.05</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>19.14</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45453</v>
+        <v>45454</v>
       </c>
       <c r="H71" t="n">
-        <v>95.31</v>
+        <v>104.39</v>
       </c>
       <c r="I71" t="n">
         <v>103.2901107644052</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>-9.93</v>
+        <v>-20.4</v>
       </c>
       <c r="L71" t="n">
-        <v>11.88</v>
+        <v>22.64</v>
       </c>
       <c r="M71" t="n">
         <v>5.16</v>
       </c>
       <c r="N71" t="n">
-        <v>6.92</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O71" t="n">
         <v>-4.09</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>19.22</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H72" t="n">
-        <v>111.91</v>
+        <v>109.19</v>
       </c>
       <c r="I72" t="n">
         <v>109.6300737657646</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K72" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="L72" t="n">
         <v>5.33</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>22.96</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H73" t="n">
-        <v>99.29000000000001</v>
+        <v>100.05</v>
       </c>
       <c r="I73" t="n">
         <v>99.71307772266721</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K73" t="n">
-        <v>9.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L73" t="n">
         <v>28.06</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>5</v>
+      </c>
+      <c r="U73" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>9.94</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H74" t="n">
-        <v>94.43000000000001</v>
+        <v>92.64</v>
       </c>
       <c r="I74" t="n">
         <v>93.59337826939705</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.62</v>
+        <v>-7.41</v>
       </c>
       <c r="L74" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="M74" t="n">
         <v>2.77</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>12.03</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H75" t="n">
-        <v>87.83</v>
+        <v>95.31</v>
       </c>
       <c r="I75" t="n">
         <v>92.08638105454853</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" t="n">
-        <v>5.19</v>
+        <v>-2.88</v>
       </c>
       <c r="L75" t="n">
-        <v>3.03</v>
+        <v>4.7</v>
       </c>
       <c r="M75" t="n">
         <v>2.01</v>
       </c>
       <c r="N75" t="n">
-        <v>6.56</v>
+        <v>8.52</v>
       </c>
       <c r="O75" t="n">
         <v>-1.9</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>17.3</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H76" t="n">
-        <v>85.75</v>
+        <v>82.11</v>
       </c>
       <c r="I76" t="n">
         <v>84.42079385109966</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K76" t="n">
-        <v>-10.03</v>
+        <v>-13.85</v>
       </c>
       <c r="L76" t="n">
-        <v>12.99</v>
+        <v>14.91</v>
       </c>
       <c r="M76" t="n">
         <v>1.64</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>18.96</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H77" t="n">
-        <v>83.73</v>
+        <v>85.36</v>
       </c>
       <c r="I77" t="n">
         <v>84.61147515652989</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.97</v>
+        <v>-3.96</v>
       </c>
       <c r="L77" t="n">
         <v>5.96</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.79</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H78" t="n">
-        <v>118.92</v>
+        <v>114.29</v>
       </c>
       <c r="I78" t="n">
         <v>115.5634972131454</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K78" t="n">
-        <v>39.32</v>
+        <v>33.89</v>
       </c>
       <c r="L78" t="n">
         <v>12.14</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>13</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H79" t="n">
-        <v>105.52</v>
+        <v>107.81</v>
       </c>
       <c r="I79" t="n">
         <v>107.5538979615264</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K79" t="n">
-        <v>7.67</v>
+        <v>5.67</v>
       </c>
       <c r="L79" t="n">
         <v>9.85</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>7.96</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H80" t="n">
-        <v>112.06</v>
+        <v>108.98</v>
       </c>
       <c r="I80" t="n">
         <v>109.3221550588553</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K80" t="n">
-        <v>3.94</v>
+        <v>1.09</v>
       </c>
       <c r="L80" t="n">
         <v>2.88</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>10.93</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="H81" t="n">
-        <v>116.16</v>
+        <v>122.06</v>
       </c>
       <c r="I81" t="n">
         <v>117.3202383247291</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K81" t="n">
-        <v>-6.59</v>
+        <v>-12</v>
       </c>
       <c r="L81" t="n">
-        <v>9.779999999999999</v>
+        <v>12.41</v>
       </c>
       <c r="M81" t="n">
         <v>2.62</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>11.42</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H82" t="n">
-        <v>116.05</v>
+        <v>112.09</v>
       </c>
       <c r="I82" t="n">
         <v>112.9574983887387</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K82" t="n">
-        <v>-4.92</v>
+        <v>-8.17</v>
       </c>
       <c r="L82" t="n">
-        <v>5.62</v>
+        <v>8.65</v>
       </c>
       <c r="M82" t="n">
         <v>0.16</v>
       </c>
       <c r="N82" t="n">
-        <v>2.46</v>
+        <v>3.41</v>
       </c>
       <c r="O82" t="n">
         <v>5.08</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>11.22</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H83" t="n">
-        <v>88.65000000000001</v>
+        <v>91</v>
       </c>
       <c r="I83" t="n">
         <v>90.20864933252042</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K83" t="n">
-        <v>20.91</v>
+        <v>18.82</v>
       </c>
       <c r="L83" t="n">
         <v>3.94</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>4</v>
+      </c>
+      <c r="U83" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>11.79</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="H84" t="n">
-        <v>102.36</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="I84" t="n">
         <v>99.87064253689272</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K84" t="n">
-        <v>12.48</v>
+        <v>9.42</v>
       </c>
       <c r="L84" t="n">
         <v>1.29</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,14 @@
       <c r="Q85" t="n">
         <v>80</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +11274,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.8</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="6">
@@ -10257,7 +11284,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -10267,7 +11294,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
@@ -10277,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10287,7 +11314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="10">
@@ -10297,7 +11324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -10307,7 +11334,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -10317,7 +11344,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10327,7 +11354,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.9</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="14">
@@ -10337,7 +11364,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.61</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="15">
@@ -10347,7 +11374,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.41</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="16">
@@ -10357,7 +11384,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.75</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="17">
@@ -10367,7 +11394,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>246.07</v>
+        <v>211.47</v>
       </c>
     </row>
     <row r="18">
@@ -10377,7 +11404,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="19">
@@ -10387,7 +11414,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.74</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="20">
@@ -10397,7 +11424,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.98</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="21">
@@ -10417,7 +11444,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -10427,7 +11454,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -10437,7 +11464,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="25">
@@ -10457,7 +11484,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
@@ -10467,7 +11494,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.06</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="28">
@@ -10477,7 +11504,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
